--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.172" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.172" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.172.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.172.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0172.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0172.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -875,7 +875,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.172" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.172" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y60"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ORDERS â€” Continued.</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ORDERSâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 165</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L32: symbol-only separator/garbage line :: . 105</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -632,7 +636,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,10 +678,14 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+559C CJK UNIFIED IDEOGRAPH-559C | isolated marker/symbol line :: 喜</t>
+        </is>
+      </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 86â€”87â€”122</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +697,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 111</t>
+          <t>L28: symbol-only separator/garbage line :: 86—87—122</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -732,7 +744,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 105</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 111</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -744,7 +756,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L36: symbol-only separator/garbage line :: . 111</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,7 +782,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -787,7 +799,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 3â€”104</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -799,7 +811,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 94</t>
+          <t>L32: symbol-only separator/garbage line :: . 105</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -840,11 +852,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 66â€”67</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -854,7 +862,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 94</t>
+          <t>L34: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -895,11 +903,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 67â€”68</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -909,7 +913,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 138</t>
+          <t>L36: symbol-only separator/garbage line :: . 111</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -950,11 +954,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ . 111</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: 138</t>
+          <t>L38: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1005,11 +1005,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1019,7 +1015,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 146</t>
+          <t>L40: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1045,12 +1041,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1060,11 +1056,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6â€”87</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1074,7 +1066,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L55: symbol-only separator/garbage line :: . 142</t>
+          <t>L46: symbol-only separator/garbage line :: 3—104</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1101,7 +1093,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1111,11 +1103,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 79â€”80â€”81</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1125,7 +1113,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L57: symbol-only separator/garbage line :: . 140</t>
+          <t>L48: isolated marker/symbol line :: 138</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1147,12 +1135,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1162,11 +1150,7 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 82â€”83</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1176,7 +1160,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 114</t>
+          <t>L50: isolated marker/symbol line :: 138</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1213,11 +1197,7 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 5â€”6</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1227,7 +1207,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: %</t>
+          <t>L53: isolated marker/symbol line :: 146</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1254,7 +1234,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1269,12 +1249,12 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: 140</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 68</t>
+          <t>L55: symbol-only separator/garbage line :: . 142</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1316,12 +1296,12 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: 142</t>
+          <t>L30: isolated marker/symbol line :: 140</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 112</t>
+          <t>L57: symbol-only separator/garbage line :: . 140</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1363,12 +1343,12 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: 114</t>
+          <t>L31: isolated marker/symbol line :: 142</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1410,12 +1390,12 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L38: symbol-only separator/garbage line :: 66-67</t>
+          <t>L35: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 110</t>
+          <t>L65: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1445,12 +1425,12 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 110</t>
+          <t>L38: symbol-only separator/garbage line :: 66-67</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: .3</t>
+          <t>L94: symbol-only separator/garbage line :: 66—67</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1480,12 +1460,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L41: symbol-only separator/garbage line :: . 68</t>
+          <t>L39: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L109: symbol-only separator/garbage line :: 3-4</t>
+          <t>L95: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1515,12 +1495,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L43: symbol-only separator/garbage line :: . 67-68</t>
+          <t>L41: symbol-only separator/garbage line :: . 68</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: - 8</t>
+          <t>L97: symbol-only separator/garbage line :: . 67—68</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1550,12 +1530,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: . 3</t>
+          <t>L43: symbol-only separator/garbage line :: . 67-68</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: 12</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 111</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1585,12 +1565,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: Â·</t>
+          <t>L44: isolated marker/symbol line :: . 3</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 155</t>
+          <t>L101: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1620,12 +1600,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L47: symbol-only separator/garbage line :: . 111</t>
+          <t>L46: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: .9</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1655,12 +1635,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L48: symbol-only separator/garbage line :: 3-4</t>
+          <t>L47: symbol-only separator/garbage line :: . 111</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 9</t>
+          <t>L105: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1690,12 +1670,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: 112</t>
+          <t>L48: symbol-only separator/garbage line :: 3-4</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 105</t>
+          <t>L107: isolated marker/symbol line :: .3</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1725,12 +1705,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L52: symbol-only separator/garbage line :: 6-87</t>
+          <t>L50: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 116</t>
+          <t>L109: symbol-only separator/garbage line :: 3-4</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1760,12 +1740,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 8</t>
+          <t>L52: symbol-only separator/garbage line :: 6-87</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 107</t>
+          <t>L111: isolated marker/symbol line :: - 8</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1795,12 +1775,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 155</t>
+          <t>L54: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L125: symbol-only separator/garbage line :: . 107</t>
+          <t>L112: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1830,12 +1810,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 12</t>
+          <t>L55: isolated marker/symbol line :: 155</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 112</t>
+          <t>L114: symbol-only separator/garbage line :: 6—87</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1865,12 +1845,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 105</t>
+          <t>L57: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 105</t>
+          <t>L115: isolated marker/symbol line :: 155</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1900,12 +1880,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 9</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+559C CJK UNIFIED IDEOGRAPH-559C | isolated marker/symbol line :: 喜</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L141: isolated marker/symbol line :: 1</t>
+          <t>L117: isolated marker/symbol line :: .9</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1935,12 +1915,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 116</t>
+          <t>L60: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: 1</t>
+          <t>L118: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1970,12 +1950,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 9</t>
+          <t>L62: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: .2</t>
+          <t>L120: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2005,10 +1985,14 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 105</t>
-        </is>
-      </c>
-      <c r="O34" s="1" t="inlineStr"/>
+          <t>L63: isolated marker/symbol line :: 116</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>L122: isolated marker/symbol line :: 116</t>
+        </is>
+      </c>
       <c r="P34" s="1" t="inlineStr"/>
       <c r="Q34" s="1" t="inlineStr"/>
       <c r="R34" s="1" t="inlineStr"/>
@@ -2036,10 +2020,14 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 107</t>
-        </is>
-      </c>
-      <c r="O35" s="1" t="inlineStr"/>
+          <t>L65: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>L124: isolated marker/symbol line :: 107</t>
+        </is>
+      </c>
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr"/>
       <c r="R35" s="1" t="inlineStr"/>
@@ -2067,10 +2055,14 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 107</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr"/>
+          <t>L67: isolated marker/symbol line :: 105</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L125: symbol-only separator/garbage line :: . 107</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2098,10 +2090,14 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 112</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr"/>
+          <t>L69: isolated marker/symbol line :: 107</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L127: isolated marker/symbol line :: 112</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2129,10 +2125,14 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="inlineStr"/>
+          <t>L71: isolated marker/symbol line :: 107</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>L139: isolated marker/symbol line :: 105</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2160,10 +2160,14 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: . 2</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr"/>
+          <t>L73: isolated marker/symbol line :: 112</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>L141: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2191,10 +2195,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L82: symbol-only separator/garbage line :: 79-80-81</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L74: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L143: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2222,10 +2230,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L83: symbol-only separator/garbage line :: 5-6</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L78: isolated marker/symbol line :: . 2</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L146: symbol-only separator/garbage line :: 79—80—81</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2253,10 +2265,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L85: symbol-only separator/garbage line :: 82-83</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L82: symbol-only separator/garbage line :: 79-80-81</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L148: symbol-only separator/garbage line :: . 82—83</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2284,10 +2300,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 94</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L83: symbol-only separator/garbage line :: 5-6</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L150: isolated marker/symbol line :: .2</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2315,10 +2335,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 94</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L85: symbol-only separator/garbage line :: 82-83</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L152: symbol-only separator/garbage line :: 5—6</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2346,7 +2370,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L92: symbol-only separator/garbage line :: 3-104</t>
+          <t>L88: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2377,7 +2401,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 138</t>
+          <t>L89: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2408,7 +2432,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 146</t>
+          <t>L92: symbol-only separator/garbage line :: 3-104</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2439,7 +2463,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 142</t>
+          <t>L93: isolated marker/symbol line :: 138</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2470,7 +2494,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L97: symbol-only separator/garbage line :: 6-87</t>
+          <t>L95: isolated marker/symbol line :: 146</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2501,7 +2525,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 155</t>
+          <t>L96: isolated marker/symbol line :: 142</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2532,7 +2556,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L99: symbol-only separator/garbage line :: 5-6</t>
+          <t>L97: symbol-only separator/garbage line :: 6-87</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2563,7 +2587,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: . 3</t>
+          <t>L98: isolated marker/symbol line :: 155</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2594,7 +2618,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L102: symbol-only separator/garbage line :: 3-4</t>
+          <t>L99: symbol-only separator/garbage line :: 5-6</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2625,7 +2649,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: . 2</t>
+          <t>L101: isolated marker/symbol line :: . 3</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -2656,7 +2680,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 105</t>
+          <t>L102: symbol-only separator/garbage line :: 3-4</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -2687,7 +2711,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 116</t>
+          <t>L103: isolated marker/symbol line :: . 2</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -2718,7 +2742,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: 105</t>
+          <t>L104: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -2749,7 +2773,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: 114</t>
+          <t>L105: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -2780,7 +2804,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 110</t>
+          <t>L106: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -2811,7 +2835,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: 1</t>
+          <t>L107: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -2826,6 +2850,68 @@
       <c r="X60" s="1" t="inlineStr"/>
       <c r="Y60" s="1" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr"/>
+      <c r="B61" s="1" t="inlineStr"/>
+      <c r="C61" s="1" t="inlineStr"/>
+      <c r="D61" s="1" t="inlineStr"/>
+      <c r="E61" s="1" t="inlineStr"/>
+      <c r="F61" s="1" t="inlineStr"/>
+      <c r="G61" s="1" t="inlineStr"/>
+      <c r="H61" s="1" t="inlineStr"/>
+      <c r="I61" s="1" t="inlineStr"/>
+      <c r="J61" s="1" t="inlineStr"/>
+      <c r="K61" s="1" t="inlineStr"/>
+      <c r="L61" s="1" t="inlineStr"/>
+      <c r="M61" s="1" t="inlineStr"/>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>L108: isolated marker/symbol line :: 110</t>
+        </is>
+      </c>
+      <c r="O61" s="1" t="inlineStr"/>
+      <c r="P61" s="1" t="inlineStr"/>
+      <c r="Q61" s="1" t="inlineStr"/>
+      <c r="R61" s="1" t="inlineStr"/>
+      <c r="S61" s="1" t="inlineStr"/>
+      <c r="T61" s="1" t="inlineStr"/>
+      <c r="U61" s="1" t="inlineStr"/>
+      <c r="V61" s="1" t="inlineStr"/>
+      <c r="W61" s="1" t="inlineStr"/>
+      <c r="X61" s="1" t="inlineStr"/>
+      <c r="Y61" s="1" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr"/>
+      <c r="B62" s="1" t="inlineStr"/>
+      <c r="C62" s="1" t="inlineStr"/>
+      <c r="D62" s="1" t="inlineStr"/>
+      <c r="E62" s="1" t="inlineStr"/>
+      <c r="F62" s="1" t="inlineStr"/>
+      <c r="G62" s="1" t="inlineStr"/>
+      <c r="H62" s="1" t="inlineStr"/>
+      <c r="I62" s="1" t="inlineStr"/>
+      <c r="J62" s="1" t="inlineStr"/>
+      <c r="K62" s="1" t="inlineStr"/>
+      <c r="L62" s="1" t="inlineStr"/>
+      <c r="M62" s="1" t="inlineStr"/>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>L109: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O62" s="1" t="inlineStr"/>
+      <c r="P62" s="1" t="inlineStr"/>
+      <c r="Q62" s="1" t="inlineStr"/>
+      <c r="R62" s="1" t="inlineStr"/>
+      <c r="S62" s="1" t="inlineStr"/>
+      <c r="T62" s="1" t="inlineStr"/>
+      <c r="U62" s="1" t="inlineStr"/>
+      <c r="V62" s="1" t="inlineStr"/>
+      <c r="W62" s="1" t="inlineStr"/>
+      <c r="X62" s="1" t="inlineStr"/>
+      <c r="Y62" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
